--- a/docs/obbbafim/OBBBAFIM.xlsx
+++ b/docs/obbbafim/OBBBAFIM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahmad\Downloads\FIM\docs\obbbafim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CParry\Downloads\FIM\docs\obbbafim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC53062-522A-43F7-A411-02643E1AC2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C3EEA0-CDF5-4E68-8690-87E814749A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{C0EAC147-CCCF-478C-A033-975E276392EF}"/>
+    <workbookView xWindow="14985" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="12" xr2:uid="{C0EAC147-CCCF-478C-A033-975E276392EF}"/>
   </bookViews>
   <sheets>
     <sheet name="To Do" sheetId="6" state="hidden" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="455">
   <si>
     <t>Link to OBBBA</t>
   </si>
@@ -1409,6 +1409,39 @@
   <si>
     <t>Calculation is in the "Effect of OBBBA Tax Provisions on Spending (Current Law)" workbook</t>
   </si>
+  <si>
+    <t>FMAP Pieces (millions) -exclude provider taxes which seem like they will be delayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider Taxes (assume these have no effect on total Medicaid as states just use their own $) </t>
+  </si>
+  <si>
+    <t>non-FMAP no-provider tax pieces</t>
+  </si>
+  <si>
+    <t>Effect on total Medicaid (assuming states save money as well on non-FMAP non-provider tax parts)</t>
+  </si>
+  <si>
+    <t>Total medicaid cut</t>
+  </si>
+  <si>
+    <t>Total Medicaid  post OBBA (forecast workbook) - FY</t>
+  </si>
+  <si>
+    <t>Rough Federal Medicaid</t>
+  </si>
+  <si>
+    <t>Medicaid no OBBA</t>
+  </si>
+  <si>
+    <t>Fed Medicaid no OBBA</t>
+  </si>
+  <si>
+    <t>New FMAP</t>
+  </si>
+  <si>
+    <t>FMAP Change (pulled into forecast)</t>
+  </si>
 </sst>
 </file>
 
@@ -1419,7 +1452,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1534,8 +1567,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1625,6 +1666,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE2D5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -1697,7 +1744,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1920,31 +1967,8 @@
     <xf numFmtId="3" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1970,13 +1994,46 @@
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1988,6 +2045,218 @@
     <cellStyle name="Normal 5" xfId="5" xr:uid="{1AE2A061-4EDA-4262-966F-D622E76A5AEF}"/>
   </cellStyles>
   <dxfs count="56">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2526,218 +2795,6 @@
         <sz val="11"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2801,82 +2858,82 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{09D7AA6F-96E4-4FB8-BD38-80A716C5D71C}" name="Table225" displayName="Table225" ref="B2:O49" totalsRowShown="0" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{09D7AA6F-96E4-4FB8-BD38-80A716C5D71C}" name="Table225" displayName="Table225" ref="B2:O49" totalsRowShown="0" dataDxfId="55">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{48923117-08ED-40BF-860A-6D35643AA53F}" name="FIM Category" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{7F48BF94-B33F-44CB-BFF6-87878CE3406B}" name="Provision" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{215933B5-DF07-4193-86B9-A9E0C36E1C37}" name="Description" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{EB1DFE9D-68EE-4AA1-A326-FFB240C3F9ED}" name="2025" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{CE7D1352-3F9D-45FA-892C-EE43C7075427}" name="2026" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{9EC9874D-53BF-4098-92B9-E35A6EE4AD08}" name="2027" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{8DE226B7-B3D1-4B3A-87A6-0D8F6E3FFF3C}" name="2028" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{024A676E-6701-41DD-A3D2-9FB4E9446B03}" name="2029" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{640E2CA0-990D-4DC1-9910-E1920163A206}" name="2030" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{8E2CD36D-6860-4E60-AB20-E5A675EFC6C9}" name="2031" dataDxfId="30"/>
-    <tableColumn id="12" xr3:uid="{61173DE1-4426-4E63-8B07-AEB2A151BE4B}" name="2032" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{E4A41F3B-E97C-49F8-8FD6-D48C03DDD347}" name="2033" dataDxfId="28"/>
-    <tableColumn id="14" xr3:uid="{ACE81429-8256-4A57-86EE-2B404336AE95}" name="2034" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{0B9044B6-57B2-4C61-9F58-740629E2C1B1}" name="2025-2034 Totals" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{48923117-08ED-40BF-860A-6D35643AA53F}" name="FIM Category" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{7F48BF94-B33F-44CB-BFF6-87878CE3406B}" name="Provision" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{215933B5-DF07-4193-86B9-A9E0C36E1C37}" name="Description" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{EB1DFE9D-68EE-4AA1-A326-FFB240C3F9ED}" name="2025" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{CE7D1352-3F9D-45FA-892C-EE43C7075427}" name="2026" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{9EC9874D-53BF-4098-92B9-E35A6EE4AD08}" name="2027" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{8DE226B7-B3D1-4B3A-87A6-0D8F6E3FFF3C}" name="2028" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{024A676E-6701-41DD-A3D2-9FB4E9446B03}" name="2029" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{640E2CA0-990D-4DC1-9910-E1920163A206}" name="2030" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{8E2CD36D-6860-4E60-AB20-E5A675EFC6C9}" name="2031" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{61173DE1-4426-4E63-8B07-AEB2A151BE4B}" name="2032" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{E4A41F3B-E97C-49F8-8FD6-D48C03DDD347}" name="2033" dataDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{ACE81429-8256-4A57-86EE-2B404336AE95}" name="2034" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{0B9044B6-57B2-4C61-9F58-740629E2C1B1}" name="2025-2034 Totals" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9B6953E-6BFB-4DBC-81A6-DE19F864DF12}" name="Table24" displayName="Table24" ref="B2:K20" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9B6953E-6BFB-4DBC-81A6-DE19F864DF12}" name="Table24" displayName="Table24" ref="B2:K20" totalsRowShown="0" dataDxfId="40">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3D36799C-C183-4AD2-BFBB-AB1992100D90}" name="FIM Category" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1AC340EA-4DBE-4C52-AF27-93AD05E57129}" name="Provision" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{730947C5-3FCC-468A-B97C-1282377F35F1}" name="Description" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{A012AC97-2F14-48AE-81F4-830CC8E2A309}" name="2025" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{023C56A1-BF9E-4143-AB00-96B144EDCA76}" name="2026" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{134CD888-8329-4E29-A894-78CD81623904}" name="2027" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{86F8C08C-AB49-4D81-9B03-2BA2D23F5E4C}" name="2028" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{F7D50089-4B29-4C31-8E86-42A6DA126DCA}" name="2029" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{4099EB1C-43F2-4100-A7CC-F3256C5C1405}" name="2030" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{0C0842DB-8B15-45A5-AD44-DA2D3A771E1E}" name="2031" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{3D36799C-C183-4AD2-BFBB-AB1992100D90}" name="FIM Category" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{1AC340EA-4DBE-4C52-AF27-93AD05E57129}" name="Provision" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{730947C5-3FCC-468A-B97C-1282377F35F1}" name="Description" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{A012AC97-2F14-48AE-81F4-830CC8E2A309}" name="2025" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{023C56A1-BF9E-4143-AB00-96B144EDCA76}" name="2026" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{134CD888-8329-4E29-A894-78CD81623904}" name="2027" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{86F8C08C-AB49-4D81-9B03-2BA2D23F5E4C}" name="2028" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{F7D50089-4B29-4C31-8E86-42A6DA126DCA}" name="2029" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{4099EB1C-43F2-4100-A7CC-F3256C5C1405}" name="2030" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{0C0842DB-8B15-45A5-AD44-DA2D3A771E1E}" name="2031" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B26E020-0EDF-4DF5-9567-C4A622782659}" name="Table2253" displayName="Table2253" ref="B2:O49" totalsRowShown="0" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B26E020-0EDF-4DF5-9567-C4A622782659}" name="Table2253" displayName="Table2253" ref="B2:O49" totalsRowShown="0" dataDxfId="29">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{67BB1EBB-B14C-4642-888A-E4FCCD9A62F7}" name="FIM Category" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{38DCD95D-E7B5-4BCA-9A5B-3B5EA1FFAD79}" name="Provision" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{581DE72C-3A0F-431E-98F1-516ECD1E1222}" name="Description" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{359643C4-104E-4A1E-BF12-5C063711291D}" name="2025" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{67BB1EBB-B14C-4642-888A-E4FCCD9A62F7}" name="FIM Category" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{38DCD95D-E7B5-4BCA-9A5B-3B5EA1FFAD79}" name="Provision" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{581DE72C-3A0F-431E-98F1-516ECD1E1222}" name="Description" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{359643C4-104E-4A1E-BF12-5C063711291D}" name="2025" dataDxfId="25">
       <calculatedColumnFormula>Table22[[#This Row],[2025]]-Table225[[#This Row],[2025]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F87C78C0-6868-4F8E-9D51-F8EC7C0A3B9A}" name="2026" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{F87C78C0-6868-4F8E-9D51-F8EC7C0A3B9A}" name="2026" dataDxfId="24">
       <calculatedColumnFormula>Table22[[#This Row],[2026]]-Table225[[#This Row],[2026]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{688122AB-8712-440C-9940-5F18D5852E09}" name="2027" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{688122AB-8712-440C-9940-5F18D5852E09}" name="2027" dataDxfId="23">
       <calculatedColumnFormula>Table22[[#This Row],[2027]]-Table225[[#This Row],[2027]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{23BC2D95-E2EA-4877-B108-85EABA57C110}" name="2028" dataDxfId="7">
+    <tableColumn id="7" xr3:uid="{23BC2D95-E2EA-4877-B108-85EABA57C110}" name="2028" dataDxfId="22">
       <calculatedColumnFormula>Table22[[#This Row],[2028]]-Table225[[#This Row],[2028]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B3043706-8A82-4192-9BAE-F7DD8CEB1816}" name="2029" dataDxfId="6">
+    <tableColumn id="8" xr3:uid="{B3043706-8A82-4192-9BAE-F7DD8CEB1816}" name="2029" dataDxfId="21">
       <calculatedColumnFormula>Table22[[#This Row],[2029]]-Table225[[#This Row],[2029]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1F941659-518C-4973-A5B2-03F5E1E1FC5C}" name="2030" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{1F941659-518C-4973-A5B2-03F5E1E1FC5C}" name="2030" dataDxfId="20">
       <calculatedColumnFormula>Table22[[#This Row],[2030]]-Table225[[#This Row],[2030]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F6D4CCF3-3D31-40FA-81A9-30EF1BC7B3DE}" name="2031" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{F6D4CCF3-3D31-40FA-81A9-30EF1BC7B3DE}" name="2031" dataDxfId="19">
       <calculatedColumnFormula>Table22[[#This Row],[2031]]-Table225[[#This Row],[2031]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E878B453-CF9D-416E-9BB0-4FAB7F9A504B}" name="2032" dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{E878B453-CF9D-416E-9BB0-4FAB7F9A504B}" name="2032" dataDxfId="18">
       <calculatedColumnFormula>Table22[[#This Row],[2032]]-Table225[[#This Row],[2032]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C7031629-1446-405A-ABCB-1B989547B743}" name="2033" dataDxfId="2">
+    <tableColumn id="13" xr3:uid="{C7031629-1446-405A-ABCB-1B989547B743}" name="2033" dataDxfId="17">
       <calculatedColumnFormula>Table22[[#This Row],[2033]]-Table225[[#This Row],[2033]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{47E72E41-A984-4C1A-A9BE-4778A7B4DD3F}" name="2034" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{47E72E41-A984-4C1A-A9BE-4778A7B4DD3F}" name="2034" dataDxfId="16">
       <calculatedColumnFormula>Table22[[#This Row],[2034]]-Table225[[#This Row],[2034]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{318D5F36-E8AD-4BF0-943D-B4FE005FE777}" name="2025-2034 Totals" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{318D5F36-E8AD-4BF0-943D-B4FE005FE777}" name="2025-2034 Totals" dataDxfId="15">
       <calculatedColumnFormula>Table22[[#This Row],[2025-2034 Totals]]-Table225[[#This Row],[2025-2034 Totals]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2885,22 +2942,22 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{370B0772-BF20-41B3-A234-8DEF1F686629}" name="Table22" displayName="Table22" ref="C2:P54" totalsRowShown="0" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{370B0772-BF20-41B3-A234-8DEF1F686629}" name="Table22" displayName="Table22" ref="C2:P54" totalsRowShown="0" dataDxfId="14">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{2108DE54-B21A-45A2-AA2E-8308DE162B3E}" name="FIM Category" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{F0A32B64-E4BF-43B4-BDDD-9D96791CB60A}" name="Provision" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{2A6DB084-C21F-44B8-A263-B9423AB6FC0D}" name="Description" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{0070D0AC-B935-4FFE-B24E-DBC4C9A8704C}" name="2025" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{8238744C-3DF5-405C-A319-D432430A741A}" name="2026" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{6F5F051F-3F36-4E07-8181-1E46487D67E0}" name="2027" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{87521439-7C68-44EC-A0E1-68D57C4825DA}" name="2028" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{3A3F8805-5702-47A7-B2B6-2528C7F2C640}" name="2029" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{5188FCE9-4D66-46B2-B066-39151BF534E0}" name="2030" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{7E0AD104-B1D1-40A4-BCF9-3BD2349AAB87}" name="2031" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{106283A5-0BF7-4FC9-8382-0713793B2478}" name="2032" dataDxfId="44"/>
-    <tableColumn id="13" xr3:uid="{003691B4-DE91-4883-B461-97EA5492813E}" name="2033" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{0406F704-2FB9-4519-A94B-39EDC0DAF482}" name="2034" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{D834C730-B466-4BE3-92DF-4266457FFCE9}" name="2025-2034 Totals" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{2108DE54-B21A-45A2-AA2E-8308DE162B3E}" name="FIM Category" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{F0A32B64-E4BF-43B4-BDDD-9D96791CB60A}" name="Provision" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{2A6DB084-C21F-44B8-A263-B9423AB6FC0D}" name="Description" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{0070D0AC-B935-4FFE-B24E-DBC4C9A8704C}" name="2025" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{8238744C-3DF5-405C-A319-D432430A741A}" name="2026" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{6F5F051F-3F36-4E07-8181-1E46487D67E0}" name="2027" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{87521439-7C68-44EC-A0E1-68D57C4825DA}" name="2028" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{3A3F8805-5702-47A7-B2B6-2528C7F2C640}" name="2029" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{5188FCE9-4D66-46B2-B066-39151BF534E0}" name="2030" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{7E0AD104-B1D1-40A4-BCF9-3BD2349AAB87}" name="2031" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{106283A5-0BF7-4FC9-8382-0713793B2478}" name="2032" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{003691B4-DE91-4883-B461-97EA5492813E}" name="2033" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{0406F704-2FB9-4519-A94B-39EDC0DAF482}" name="2034" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{D834C730-B466-4BE3-92DF-4266457FFCE9}" name="2025-2034 Totals" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3428,20 +3485,20 @@
       <c r="A1" s="86" t="s">
         <v>286</v>
       </c>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="128" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
     </row>
     <row r="2" spans="1:15" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -7499,20 +7556,20 @@
       <c r="A96" s="86" t="s">
         <v>325</v>
       </c>
-      <c r="D96" s="118" t="s">
+      <c r="D96" s="134" t="s">
         <v>326</v>
       </c>
-      <c r="E96" s="118"/>
-      <c r="F96" s="118"/>
-      <c r="G96" s="118"/>
-      <c r="H96" s="118"/>
-      <c r="I96" s="118"/>
-      <c r="J96" s="118"/>
-      <c r="K96" s="118"/>
-      <c r="L96" s="118"/>
-      <c r="M96" s="118"/>
-      <c r="N96" s="118"/>
-      <c r="O96" s="118"/>
+      <c r="E96" s="134"/>
+      <c r="F96" s="134"/>
+      <c r="G96" s="134"/>
+      <c r="H96" s="134"/>
+      <c r="I96" s="134"/>
+      <c r="J96" s="134"/>
+      <c r="K96" s="134"/>
+      <c r="L96" s="134"/>
+      <c r="M96" s="134"/>
+      <c r="N96" s="134"/>
+      <c r="O96" s="134"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
@@ -8012,20 +8069,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="128" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
     </row>
     <row r="2" spans="1:16" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -11088,20 +11145,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="128" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
     </row>
     <row r="2" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -11480,7 +11537,7 @@
       <c r="A10">
         <v>71108</v>
       </c>
-      <c r="B10" s="121" t="s">
+      <c r="B10" t="s">
         <v>342</v>
       </c>
       <c r="C10" s="30">
@@ -11527,7 +11584,7 @@
       <c r="A11">
         <v>71109</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" t="s">
         <v>343</v>
       </c>
       <c r="C11" s="30">
@@ -11574,7 +11631,7 @@
       <c r="A12">
         <v>71110</v>
       </c>
-      <c r="B12" s="121" t="s">
+      <c r="B12" t="s">
         <v>344</v>
       </c>
       <c r="C12" s="30">
@@ -11621,7 +11678,7 @@
       <c r="A13">
         <v>71111</v>
       </c>
-      <c r="B13" s="121" t="s">
+      <c r="B13" t="s">
         <v>345</v>
       </c>
       <c r="C13" s="30">
@@ -11668,7 +11725,7 @@
       <c r="A14">
         <v>71112</v>
       </c>
-      <c r="B14" s="134" t="s">
+      <c r="B14" s="125" t="s">
         <v>346</v>
       </c>
       <c r="C14" s="30">
@@ -11715,7 +11772,7 @@
       <c r="A15">
         <v>71113</v>
       </c>
-      <c r="B15" s="134" t="s">
+      <c r="B15" s="125" t="s">
         <v>347</v>
       </c>
       <c r="C15" s="30">
@@ -11762,7 +11819,7 @@
       <c r="A16">
         <v>71114</v>
       </c>
-      <c r="B16" s="121" t="s">
+      <c r="B16" t="s">
         <v>348</v>
       </c>
       <c r="C16" s="81">
@@ -11809,7 +11866,7 @@
       <c r="A17">
         <v>71115</v>
       </c>
-      <c r="B17" s="134" t="s">
+      <c r="B17" s="125" t="s">
         <v>349</v>
       </c>
       <c r="C17" s="30">
@@ -11856,7 +11913,7 @@
       <c r="A18">
         <v>71116</v>
       </c>
-      <c r="B18" s="134" t="s">
+      <c r="B18" s="125" t="s">
         <v>350</v>
       </c>
       <c r="C18" s="30">
@@ -11903,7 +11960,7 @@
       <c r="A19">
         <v>71117</v>
       </c>
-      <c r="B19" s="121" t="s">
+      <c r="B19" t="s">
         <v>351</v>
       </c>
       <c r="C19" s="30">
@@ -11950,7 +12007,7 @@
       <c r="A20">
         <v>71119</v>
       </c>
-      <c r="B20" s="121" t="s">
+      <c r="B20" t="s">
         <v>352</v>
       </c>
       <c r="C20" s="30">
@@ -11997,7 +12054,7 @@
       <c r="A21">
         <v>71120</v>
       </c>
-      <c r="B21" s="121" t="s">
+      <c r="B21" t="s">
         <v>353</v>
       </c>
       <c r="C21" s="30">
@@ -12088,162 +12145,230 @@
       <c r="O22" s="81"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B23" s="135" t="s">
+      <c r="A23" s="30"/>
+      <c r="B23" s="126" t="s">
         <v>436</v>
       </c>
       <c r="C23" s="14">
-        <f t="shared" ref="C23:N23" si="2">SUM(C3:C22)</f>
         <v>-45</v>
       </c>
       <c r="D23" s="14">
-        <f t="shared" si="2"/>
         <v>-18549</v>
       </c>
       <c r="E23" s="14">
-        <f t="shared" si="2"/>
         <v>-49965</v>
       </c>
       <c r="F23" s="14">
-        <f t="shared" si="2"/>
         <v>-66999</v>
       </c>
       <c r="G23" s="14">
-        <f t="shared" si="2"/>
         <v>-99932</v>
       </c>
       <c r="H23" s="14">
-        <f t="shared" si="2"/>
         <v>-120278</v>
       </c>
       <c r="I23" s="14">
-        <f t="shared" si="2"/>
         <v>-139006</v>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="2"/>
         <v>-150722</v>
       </c>
       <c r="K23" s="14">
-        <f t="shared" si="2"/>
         <v>-162612</v>
       </c>
       <c r="L23" s="14">
-        <f t="shared" si="2"/>
         <v>-178387</v>
       </c>
       <c r="M23" s="14">
-        <f t="shared" si="2"/>
         <v>-235490</v>
       </c>
       <c r="N23" s="14">
-        <f t="shared" si="2"/>
         <v>-986495</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="30"/>
       <c r="B24" s="135" t="s">
-        <v>437</v>
-      </c>
-      <c r="C24" s="119">
-        <f t="shared" ref="C24:N24" si="3">C23/1000</f>
-        <v>-4.4999999999999998E-2</v>
-      </c>
-      <c r="D24" s="119">
-        <f t="shared" si="3"/>
-        <v>-18.548999999999999</v>
-      </c>
-      <c r="E24" s="14">
-        <f t="shared" si="3"/>
-        <v>-49.965000000000003</v>
-      </c>
-      <c r="F24" s="14">
-        <f t="shared" si="3"/>
-        <v>-66.998999999999995</v>
-      </c>
-      <c r="G24" s="14">
-        <f t="shared" si="3"/>
-        <v>-99.932000000000002</v>
-      </c>
-      <c r="H24" s="14">
-        <f t="shared" si="3"/>
-        <v>-120.27800000000001</v>
-      </c>
-      <c r="I24" s="14">
-        <f t="shared" si="3"/>
-        <v>-139.006</v>
-      </c>
-      <c r="J24" s="14">
-        <f t="shared" si="3"/>
-        <v>-150.72200000000001</v>
-      </c>
-      <c r="K24" s="14">
-        <f t="shared" si="3"/>
-        <v>-162.61199999999999</v>
-      </c>
-      <c r="L24" s="14">
-        <f t="shared" si="3"/>
-        <v>-178.387</v>
-      </c>
-      <c r="M24" s="14">
-        <f t="shared" si="3"/>
-        <v>-235.49</v>
-      </c>
-      <c r="N24" s="14">
-        <f t="shared" si="3"/>
-        <v>-986.495</v>
+        <v>444</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>-953</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-3819</v>
+      </c>
+      <c r="F24" s="15">
+        <v>-4518</v>
+      </c>
+      <c r="G24" s="15">
+        <v>-4765</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-5011</v>
+      </c>
+      <c r="I24" s="15">
+        <v>-5271</v>
+      </c>
+      <c r="J24" s="15">
+        <v>-5539</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-5829</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-6124</v>
+      </c>
+      <c r="M24" s="15">
+        <v>-41472</v>
+      </c>
+      <c r="N24" s="15">
+        <v>-232947</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="15"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="135" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15">
+        <v>-2786</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-4737</v>
+      </c>
+      <c r="F25" s="15">
+        <v>-7600</v>
+      </c>
+      <c r="G25" s="15">
+        <v>-12294</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-18585</v>
+      </c>
+      <c r="I25" s="15">
+        <v>-26724</v>
+      </c>
+      <c r="J25" s="15">
+        <v>-34099</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-39317</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-44976</v>
+      </c>
+      <c r="M25" s="15">
+        <v>-27417</v>
+      </c>
+      <c r="N25" s="15">
+        <v>-191118</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="135" t="s">
+        <v>446</v>
+      </c>
+      <c r="C26" s="14">
+        <v>-45</v>
+      </c>
+      <c r="D26" s="15">
+        <v>-14810</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-41409</v>
+      </c>
+      <c r="F26" s="15">
+        <v>-54881</v>
+      </c>
+      <c r="G26" s="15">
+        <v>-82873</v>
+      </c>
+      <c r="H26" s="15">
+        <v>-96682</v>
+      </c>
+      <c r="I26" s="15">
+        <v>-107011</v>
+      </c>
+      <c r="J26" s="15">
+        <v>-111084</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-117466</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-127287</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-166601</v>
+      </c>
+      <c r="N26" s="15">
+        <v>-562430</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="135" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="14">
+        <v>-65</v>
+      </c>
+      <c r="D27" s="15">
+        <v>-21464</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-60013</v>
+      </c>
+      <c r="F27" s="15">
+        <v>-79538</v>
+      </c>
+      <c r="G27" s="15">
+        <v>-120106</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-140119</v>
+      </c>
+      <c r="I27" s="15">
+        <v>-155088</v>
+      </c>
+      <c r="J27" s="15">
+        <v>-160991</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-170241</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-184474</v>
+      </c>
+      <c r="M27" s="15">
+        <v>-241451</v>
+      </c>
+      <c r="N27" s="15">
+        <v>-815116</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="13"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="135" t="s">
+        <v>448</v>
+      </c>
       <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="D28" s="136">
+        <v>-0.02</v>
+      </c>
+      <c r="E28" s="136">
+        <v>-0.06</v>
+      </c>
+      <c r="F28" s="136">
+        <v>-7.0000000000000007E-2</v>
+      </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
@@ -12254,171 +12379,232 @@
       <c r="N28" s="14"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="13"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="81"/>
-      <c r="N29" s="81"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="135"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B30" s="13"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="97"/>
-      <c r="N30" s="97"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="135"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="13"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="97"/>
-      <c r="N31" s="97"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="135"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B32" s="13"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="97"/>
-      <c r="N32" s="97"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="13"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="135"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="30"/>
+      <c r="B33" s="135" t="s">
+        <v>449</v>
+      </c>
       <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="D33" s="15">
+        <v>1059000</v>
+      </c>
+      <c r="E33" s="15">
+        <v>1085000</v>
+      </c>
+      <c r="F33" s="15">
+        <v>1174000</v>
+      </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="K33" s="14"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="13"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="30"/>
+      <c r="B34" s="135" t="s">
+        <v>450</v>
+      </c>
       <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="13"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B36" s="13"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="97"/>
-      <c r="N36" s="97"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="13"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="15"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="D34" s="14">
+        <v>730710</v>
+      </c>
+      <c r="E34" s="14">
+        <v>748650</v>
+      </c>
+      <c r="F34" s="14">
+        <v>810060</v>
+      </c>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="30"/>
+      <c r="B35" s="135" t="s">
+        <v>451</v>
+      </c>
+      <c r="C35" s="14">
+        <v>65</v>
+      </c>
+      <c r="D35" s="15">
+        <v>1080464</v>
+      </c>
+      <c r="E35" s="15">
+        <v>1145013</v>
+      </c>
+      <c r="F35" s="15">
+        <v>1253538</v>
+      </c>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="30"/>
+      <c r="B36" s="135" t="s">
+        <v>452</v>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="32">
+        <v>749259</v>
+      </c>
+      <c r="E36" s="32">
+        <v>798615</v>
+      </c>
+      <c r="F36" s="32">
+        <v>877059</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="30"/>
+      <c r="B37" s="135"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="76"/>
+      <c r="N37" s="76"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="30"/>
+      <c r="B38" s="135" t="s">
+        <v>453</v>
+      </c>
+      <c r="C38" s="76"/>
+      <c r="D38" s="137">
+        <v>0.6895</v>
+      </c>
+      <c r="E38" s="137">
+        <v>0.68940000000000001</v>
+      </c>
+      <c r="F38" s="137">
+        <v>0.68940000000000001</v>
+      </c>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="76"/>
+      <c r="N38" s="76"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="30"/>
+      <c r="B39" s="138" t="s">
+        <v>454</v>
+      </c>
+      <c r="C39" s="139"/>
+      <c r="D39" s="140">
+        <v>-5.0000000000000001E-4</v>
+      </c>
+      <c r="E39" s="140">
+        <v>-5.9999999999999995E-4</v>
+      </c>
+      <c r="F39" s="140">
+        <v>-5.9999999999999995E-4</v>
+      </c>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="76"/>
+      <c r="N39" s="76"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B40" s="13"/>
       <c r="C40" s="14"/>
       <c r="D40" s="15"/>
@@ -12433,7 +12619,7 @@
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B41" s="13"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -12448,7 +12634,7 @@
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B42" s="13"/>
       <c r="C42" s="14"/>
       <c r="D42" s="15"/>
@@ -12463,7 +12649,7 @@
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
       <c r="D43" s="15"/>
@@ -12478,7 +12664,7 @@
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B44" s="13"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -12493,7 +12679,7 @@
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B45" s="13"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -12508,7 +12694,7 @@
       <c r="M45" s="14"/>
       <c r="N45" s="15"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B46" s="13"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -12523,7 +12709,7 @@
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B47" s="13"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -12538,7 +12724,7 @@
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B48" s="13"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -13134,18 +13320,18 @@
       <c r="N91" s="97"/>
     </row>
     <row r="95" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C95" s="113"/>
-      <c r="D95" s="113"/>
-      <c r="E95" s="113"/>
-      <c r="F95" s="113"/>
-      <c r="G95" s="113"/>
-      <c r="H95" s="113"/>
-      <c r="I95" s="113"/>
-      <c r="J95" s="113"/>
-      <c r="K95" s="113"/>
-      <c r="L95" s="113"/>
-      <c r="M95" s="113"/>
-      <c r="N95" s="113"/>
+      <c r="C95" s="128"/>
+      <c r="D95" s="128"/>
+      <c r="E95" s="128"/>
+      <c r="F95" s="128"/>
+      <c r="G95" s="128"/>
+      <c r="H95" s="128"/>
+      <c r="I95" s="128"/>
+      <c r="J95" s="128"/>
+      <c r="K95" s="128"/>
+      <c r="L95" s="128"/>
+      <c r="M95" s="128"/>
+      <c r="N95" s="128"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B96" s="13"/>
@@ -13258,9 +13444,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="26" x14ac:dyDescent="0.35">
-      <c r="A1" s="123"/>
-      <c r="B1" s="124"/>
-      <c r="C1" s="125"/>
+      <c r="A1" s="114"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="116"/>
       <c r="D1" s="57">
         <v>2025</v>
       </c>
@@ -13299,9 +13485,9 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
       <c r="D2" s="83"/>
       <c r="E2" s="83"/>
       <c r="F2" s="83"/>
@@ -13312,32 +13498,32 @@
       <c r="K2" s="83"/>
       <c r="L2" s="83"/>
       <c r="M2" s="83"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="126"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="117" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="133" t="s">
         <v>365</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
     </row>
     <row r="4" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="123"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="125"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
       <c r="D4" s="83"/>
       <c r="E4" s="83"/>
       <c r="F4" s="83"/>
@@ -13348,47 +13534,47 @@
       <c r="K4" s="83"/>
       <c r="L4" s="83"/>
       <c r="M4" s="83"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="123" t="s">
+      <c r="A5" s="114" t="s">
         <v>366</v>
       </c>
-      <c r="B5" s="123">
+      <c r="B5" s="114">
         <v>20001</v>
       </c>
-      <c r="C5" s="123" t="s">
+      <c r="C5" s="114" t="s">
         <v>367</v>
       </c>
       <c r="D5" s="9">
         <v>0</v>
       </c>
-      <c r="E5" s="127">
-        <v>0</v>
-      </c>
-      <c r="F5" s="127">
-        <v>0</v>
-      </c>
-      <c r="G5" s="127">
+      <c r="E5" s="118">
+        <v>0</v>
+      </c>
+      <c r="F5" s="118">
+        <v>0</v>
+      </c>
+      <c r="G5" s="118">
         <v>-167</v>
       </c>
-      <c r="H5" s="127">
+      <c r="H5" s="118">
         <v>-163</v>
       </c>
-      <c r="I5" s="127">
+      <c r="I5" s="118">
         <v>-148</v>
       </c>
-      <c r="J5" s="127">
+      <c r="J5" s="118">
         <v>-133</v>
       </c>
-      <c r="K5" s="127">
+      <c r="K5" s="118">
         <v>-118</v>
       </c>
-      <c r="L5" s="127">
+      <c r="L5" s="118">
         <v>-74</v>
       </c>
-      <c r="M5" s="127">
+      <c r="M5" s="118">
         <v>0</v>
       </c>
       <c r="N5" s="82">
@@ -13399,41 +13585,41 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="123"/>
-      <c r="B6" s="128">
+      <c r="A6" s="114"/>
+      <c r="B6" s="119">
         <v>20002</v>
       </c>
       <c r="C6" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="127">
+      <c r="D6" s="118">
         <v>155</v>
       </c>
-      <c r="E6" s="127">
+      <c r="E6" s="118">
         <v>3726</v>
       </c>
-      <c r="F6" s="127">
+      <c r="F6" s="118">
         <v>6219</v>
       </c>
-      <c r="G6" s="127">
+      <c r="G6" s="118">
         <v>5198</v>
       </c>
-      <c r="H6" s="127">
+      <c r="H6" s="118">
         <v>4508</v>
       </c>
-      <c r="I6" s="127">
+      <c r="I6" s="118">
         <v>3045</v>
       </c>
-      <c r="J6" s="127">
+      <c r="J6" s="118">
         <v>1864</v>
       </c>
-      <c r="K6" s="127">
+      <c r="K6" s="118">
         <v>1373</v>
       </c>
-      <c r="L6" s="127">
+      <c r="L6" s="118">
         <v>911</v>
       </c>
-      <c r="M6" s="127">
+      <c r="M6" s="118">
         <v>552</v>
       </c>
       <c r="N6" s="82">
@@ -13444,41 +13630,41 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="123"/>
-      <c r="B7" s="128">
+      <c r="A7" s="114"/>
+      <c r="B7" s="119">
         <v>20003</v>
       </c>
-      <c r="C7" s="123" t="s">
+      <c r="C7" s="114" t="s">
         <v>369</v>
       </c>
-      <c r="D7" s="127">
+      <c r="D7" s="118">
         <v>212</v>
       </c>
-      <c r="E7" s="127">
+      <c r="E7" s="118">
         <v>5226</v>
       </c>
-      <c r="F7" s="127">
+      <c r="F7" s="118">
         <v>8284</v>
       </c>
-      <c r="G7" s="127">
+      <c r="G7" s="118">
         <v>4123</v>
       </c>
-      <c r="H7" s="127">
+      <c r="H7" s="118">
         <v>3073</v>
       </c>
-      <c r="I7" s="127">
+      <c r="I7" s="118">
         <v>1370</v>
       </c>
-      <c r="J7" s="127">
+      <c r="J7" s="118">
         <v>589</v>
       </c>
-      <c r="K7" s="127">
+      <c r="K7" s="118">
         <v>211</v>
       </c>
-      <c r="L7" s="127">
+      <c r="L7" s="118">
         <v>89</v>
       </c>
-      <c r="M7" s="127">
+      <c r="M7" s="118">
         <v>19</v>
       </c>
       <c r="N7" s="82">
@@ -13489,40 +13675,40 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="128">
+      <c r="B8" s="119">
         <v>20004</v>
       </c>
-      <c r="C8" s="123" t="s">
+      <c r="C8" s="114" t="s">
         <v>370</v>
       </c>
-      <c r="D8" s="127">
+      <c r="D8" s="118">
         <v>138</v>
       </c>
-      <c r="E8" s="127">
+      <c r="E8" s="118">
         <v>3537</v>
       </c>
-      <c r="F8" s="127">
+      <c r="F8" s="118">
         <v>6221</v>
       </c>
-      <c r="G8" s="127">
+      <c r="G8" s="118">
         <v>5668</v>
       </c>
-      <c r="H8" s="127">
+      <c r="H8" s="118">
         <v>4171</v>
       </c>
-      <c r="I8" s="127">
+      <c r="I8" s="118">
         <v>2438</v>
       </c>
-      <c r="J8" s="127">
+      <c r="J8" s="118">
         <v>977</v>
       </c>
-      <c r="K8" s="127">
+      <c r="K8" s="118">
         <v>578</v>
       </c>
-      <c r="L8" s="127">
+      <c r="L8" s="118">
         <v>71</v>
       </c>
-      <c r="M8" s="127">
+      <c r="M8" s="118">
         <v>0</v>
       </c>
       <c r="N8" s="82">
@@ -13533,40 +13719,40 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B9" s="128">
+      <c r="B9" s="119">
         <v>20005</v>
       </c>
-      <c r="C9" s="123" t="s">
+      <c r="C9" s="114" t="s">
         <v>371</v>
       </c>
-      <c r="D9" s="127">
+      <c r="D9" s="118">
         <v>301</v>
       </c>
-      <c r="E9" s="127">
+      <c r="E9" s="118">
         <v>7111</v>
       </c>
-      <c r="F9" s="127">
+      <c r="F9" s="118">
         <v>6197</v>
       </c>
-      <c r="G9" s="127">
+      <c r="G9" s="118">
         <v>1390</v>
       </c>
-      <c r="H9" s="127">
+      <c r="H9" s="118">
         <v>290</v>
       </c>
-      <c r="I9" s="127">
+      <c r="I9" s="118">
         <v>155</v>
       </c>
-      <c r="J9" s="127">
+      <c r="J9" s="118">
         <v>13</v>
       </c>
-      <c r="K9" s="127">
+      <c r="K9" s="118">
         <v>3</v>
       </c>
-      <c r="L9" s="127">
+      <c r="L9" s="118">
         <v>2</v>
       </c>
-      <c r="M9" s="127">
+      <c r="M9" s="118">
         <v>0</v>
       </c>
       <c r="N9" s="82">
@@ -13577,40 +13763,40 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="128">
+      <c r="B10" s="119">
         <v>20006</v>
       </c>
-      <c r="C10" s="123" t="s">
+      <c r="C10" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="D10" s="127">
+      <c r="D10" s="118">
         <v>10</v>
       </c>
-      <c r="E10" s="127">
+      <c r="E10" s="118">
         <v>233</v>
       </c>
-      <c r="F10" s="127">
+      <c r="F10" s="118">
         <v>109</v>
       </c>
-      <c r="G10" s="127">
+      <c r="G10" s="118">
         <v>10</v>
       </c>
-      <c r="H10" s="127">
+      <c r="H10" s="118">
         <v>1</v>
       </c>
-      <c r="I10" s="127">
+      <c r="I10" s="118">
         <v>1</v>
       </c>
-      <c r="J10" s="127">
-        <v>0</v>
-      </c>
-      <c r="K10" s="127">
-        <v>0</v>
-      </c>
-      <c r="L10" s="127">
-        <v>0</v>
-      </c>
-      <c r="M10" s="127">
+      <c r="J10" s="118">
+        <v>0</v>
+      </c>
+      <c r="K10" s="118">
+        <v>0</v>
+      </c>
+      <c r="L10" s="118">
+        <v>0</v>
+      </c>
+      <c r="M10" s="118">
         <v>0</v>
       </c>
       <c r="N10" s="82">
@@ -13621,40 +13807,40 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="128">
+      <c r="B11" s="119">
         <v>20007</v>
       </c>
-      <c r="C11" s="123" t="s">
+      <c r="C11" s="114" t="s">
         <v>373</v>
       </c>
-      <c r="D11" s="127">
+      <c r="D11" s="118">
         <v>68</v>
       </c>
-      <c r="E11" s="127">
+      <c r="E11" s="118">
         <v>1699</v>
       </c>
-      <c r="F11" s="127">
+      <c r="F11" s="118">
         <v>2336</v>
       </c>
-      <c r="G11" s="127">
+      <c r="G11" s="118">
         <v>1864</v>
       </c>
-      <c r="H11" s="127">
+      <c r="H11" s="118">
         <v>1244</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="118">
         <v>537</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="118">
         <v>256</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="118">
         <v>101</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="118">
         <v>68</v>
       </c>
-      <c r="M11" s="127">
+      <c r="M11" s="118">
         <v>0</v>
       </c>
       <c r="N11" s="82">
@@ -13665,40 +13851,40 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="129">
+      <c r="B12" s="120">
         <v>20008</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="114" t="s">
         <v>374</v>
       </c>
-      <c r="D12" s="127">
+      <c r="D12" s="118">
         <v>210</v>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="118">
         <v>5081</v>
       </c>
-      <c r="F12" s="127">
+      <c r="F12" s="118">
         <v>4464</v>
       </c>
-      <c r="G12" s="127">
+      <c r="G12" s="118">
         <v>2388</v>
       </c>
-      <c r="H12" s="127">
+      <c r="H12" s="118">
         <v>1139</v>
       </c>
-      <c r="I12" s="127">
+      <c r="I12" s="118">
         <v>491</v>
       </c>
-      <c r="J12" s="127">
+      <c r="J12" s="118">
         <v>245</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="118">
         <v>88</v>
       </c>
-      <c r="L12" s="127">
+      <c r="L12" s="118">
         <v>55</v>
       </c>
-      <c r="M12" s="127">
+      <c r="M12" s="118">
         <v>1</v>
       </c>
       <c r="N12" s="82">
@@ -13709,40 +13895,40 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="128">
+      <c r="B13" s="119">
         <v>20009</v>
       </c>
-      <c r="C13" s="123" t="s">
+      <c r="C13" s="114" t="s">
         <v>375</v>
       </c>
-      <c r="D13" s="127">
+      <c r="D13" s="118">
         <v>192</v>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="118">
         <v>4594</v>
       </c>
-      <c r="F13" s="127">
+      <c r="F13" s="118">
         <v>4073</v>
       </c>
-      <c r="G13" s="127">
+      <c r="G13" s="118">
         <v>1583</v>
       </c>
-      <c r="H13" s="127">
+      <c r="H13" s="118">
         <v>964</v>
       </c>
-      <c r="I13" s="127">
+      <c r="I13" s="118">
         <v>400</v>
       </c>
-      <c r="J13" s="127">
+      <c r="J13" s="118">
         <v>167</v>
       </c>
-      <c r="K13" s="127">
+      <c r="K13" s="118">
         <v>69</v>
       </c>
-      <c r="L13" s="127">
+      <c r="L13" s="118">
         <v>22</v>
       </c>
-      <c r="M13" s="127">
+      <c r="M13" s="118">
         <v>6</v>
       </c>
       <c r="N13" s="82">
@@ -13753,40 +13939,40 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="128">
+      <c r="B14" s="119">
         <v>20010</v>
       </c>
-      <c r="C14" s="123" t="s">
+      <c r="C14" s="114" t="s">
         <v>376</v>
       </c>
-      <c r="D14" s="127">
+      <c r="D14" s="118">
         <v>237</v>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="118">
         <v>5646</v>
       </c>
-      <c r="F14" s="127">
+      <c r="F14" s="118">
         <v>4511</v>
       </c>
-      <c r="G14" s="127">
+      <c r="G14" s="118">
         <v>2404</v>
       </c>
-      <c r="H14" s="127">
+      <c r="H14" s="118">
         <v>1463</v>
       </c>
-      <c r="I14" s="127">
+      <c r="I14" s="118">
         <v>634</v>
       </c>
-      <c r="J14" s="127">
+      <c r="J14" s="118">
         <v>332</v>
       </c>
-      <c r="K14" s="127">
+      <c r="K14" s="118">
         <v>180</v>
       </c>
-      <c r="L14" s="127">
+      <c r="L14" s="118">
         <v>59</v>
       </c>
-      <c r="M14" s="127">
+      <c r="M14" s="118">
         <v>15</v>
       </c>
       <c r="N14" s="82">
@@ -13797,40 +13983,40 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="128">
+      <c r="B15" s="119">
         <v>20011</v>
       </c>
-      <c r="C15" s="123" t="s">
+      <c r="C15" s="114" t="s">
         <v>377</v>
       </c>
-      <c r="D15" s="127">
+      <c r="D15" s="118">
         <v>31</v>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="118">
         <v>714</v>
       </c>
-      <c r="F15" s="127">
+      <c r="F15" s="118">
         <v>192</v>
       </c>
-      <c r="G15" s="127">
+      <c r="G15" s="118">
         <v>23</v>
       </c>
-      <c r="H15" s="127">
+      <c r="H15" s="118">
         <v>8</v>
       </c>
-      <c r="I15" s="127">
+      <c r="I15" s="118">
         <v>4</v>
       </c>
-      <c r="J15" s="127">
+      <c r="J15" s="118">
         <v>2</v>
       </c>
-      <c r="K15" s="127">
-        <v>0</v>
-      </c>
-      <c r="L15" s="127">
-        <v>0</v>
-      </c>
-      <c r="M15" s="127">
+      <c r="K15" s="118">
+        <v>0</v>
+      </c>
+      <c r="L15" s="118">
+        <v>0</v>
+      </c>
+      <c r="M15" s="118">
         <v>0</v>
       </c>
       <c r="N15" s="82">
@@ -13841,40 +14027,40 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="128">
+      <c r="B16" s="119">
         <v>20012</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="114" t="s">
         <v>378</v>
       </c>
-      <c r="D16" s="127">
-        <v>0</v>
-      </c>
-      <c r="E16" s="127">
+      <c r="D16" s="118">
+        <v>0</v>
+      </c>
+      <c r="E16" s="118">
         <v>2</v>
       </c>
-      <c r="F16" s="127">
+      <c r="F16" s="118">
         <v>1</v>
       </c>
-      <c r="G16" s="127">
+      <c r="G16" s="118">
         <v>3</v>
       </c>
-      <c r="H16" s="127">
+      <c r="H16" s="118">
         <v>3</v>
       </c>
-      <c r="I16" s="127">
-        <v>0</v>
-      </c>
-      <c r="J16" s="127">
-        <v>0</v>
-      </c>
-      <c r="K16" s="127">
-        <v>0</v>
-      </c>
-      <c r="L16" s="127">
-        <v>0</v>
-      </c>
-      <c r="M16" s="127">
+      <c r="I16" s="118">
+        <v>0</v>
+      </c>
+      <c r="J16" s="118">
+        <v>0</v>
+      </c>
+      <c r="K16" s="118">
+        <v>0</v>
+      </c>
+      <c r="L16" s="118">
+        <v>0</v>
+      </c>
+      <c r="M16" s="118">
         <v>0</v>
       </c>
       <c r="N16" s="82">
@@ -13885,43 +14071,43 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="123" t="s">
+      <c r="A17" s="114" t="s">
         <v>379</v>
       </c>
-      <c r="B17" s="128">
+      <c r="B17" s="119">
         <v>30001</v>
       </c>
-      <c r="C17" s="123" t="s">
+      <c r="C17" s="114" t="s">
         <v>380</v>
       </c>
-      <c r="D17" s="127">
-        <v>0</v>
-      </c>
-      <c r="E17" s="127">
+      <c r="D17" s="118">
+        <v>0</v>
+      </c>
+      <c r="E17" s="118">
         <v>-123</v>
       </c>
-      <c r="F17" s="127">
+      <c r="F17" s="118">
         <v>-193</v>
       </c>
-      <c r="G17" s="127">
+      <c r="G17" s="118">
         <v>-189</v>
       </c>
-      <c r="H17" s="127">
+      <c r="H17" s="118">
         <v>-193</v>
       </c>
-      <c r="I17" s="127">
+      <c r="I17" s="118">
         <v>-210</v>
       </c>
-      <c r="J17" s="127">
+      <c r="J17" s="118">
         <v>-231</v>
       </c>
-      <c r="K17" s="127">
+      <c r="K17" s="118">
         <v>-262</v>
       </c>
-      <c r="L17" s="127">
+      <c r="L17" s="118">
         <v>-296</v>
       </c>
-      <c r="M17" s="127">
+      <c r="M17" s="118">
         <v>-323</v>
       </c>
       <c r="N17" s="82">
@@ -13932,122 +14118,122 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="123"/>
-      <c r="B18" s="123">
+      <c r="A18" s="114"/>
+      <c r="B18" s="114">
         <v>30002</v>
       </c>
-      <c r="C18" s="123" t="s">
+      <c r="C18" s="114" t="s">
         <v>381</v>
       </c>
-      <c r="D18" s="127">
+      <c r="D18" s="118">
         <v>-16</v>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="118">
         <v>-21</v>
       </c>
-      <c r="F18" s="127">
+      <c r="F18" s="118">
         <v>-27</v>
       </c>
-      <c r="G18" s="127">
+      <c r="G18" s="118">
         <v>-34</v>
       </c>
-      <c r="H18" s="127">
+      <c r="H18" s="118">
         <v>-27</v>
       </c>
-      <c r="I18" s="127">
+      <c r="I18" s="118">
         <v>-10</v>
       </c>
-      <c r="J18" s="127">
+      <c r="J18" s="118">
         <v>-3</v>
       </c>
-      <c r="K18" s="127">
-        <v>0</v>
-      </c>
-      <c r="L18" s="127">
-        <v>0</v>
-      </c>
-      <c r="M18" s="127">
+      <c r="K18" s="118">
+        <v>0</v>
+      </c>
+      <c r="L18" s="118">
+        <v>0</v>
+      </c>
+      <c r="M18" s="118">
         <v>0</v>
       </c>
       <c r="N18" s="82"/>
       <c r="O18" s="82"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="123"/>
-      <c r="B19" s="123">
+      <c r="A19" s="114"/>
+      <c r="B19" s="114">
         <v>30003</v>
       </c>
-      <c r="C19" s="123" t="s">
+      <c r="C19" s="114" t="s">
         <v>382</v>
       </c>
-      <c r="D19" s="127">
+      <c r="D19" s="118">
         <v>-1</v>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="118">
         <v>-44</v>
       </c>
-      <c r="F19" s="127">
+      <c r="F19" s="118">
         <v>-50</v>
       </c>
-      <c r="G19" s="127">
+      <c r="G19" s="118">
         <v>-50</v>
       </c>
-      <c r="H19" s="127">
+      <c r="H19" s="118">
         <v>-50</v>
       </c>
-      <c r="I19" s="127">
+      <c r="I19" s="118">
         <v>-50</v>
       </c>
-      <c r="J19" s="127">
+      <c r="J19" s="118">
         <v>-50</v>
       </c>
-      <c r="K19" s="127">
+      <c r="K19" s="118">
         <v>-51</v>
       </c>
-      <c r="L19" s="127">
+      <c r="L19" s="118">
         <v>-51</v>
       </c>
-      <c r="M19" s="127">
+      <c r="M19" s="118">
         <v>-51</v>
       </c>
       <c r="N19" s="82"/>
       <c r="O19" s="82"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="128">
+      <c r="B20" s="119">
         <v>30004</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="114" t="s">
         <v>383</v>
       </c>
       <c r="D20" s="9">
         <v>2</v>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="118">
         <v>56</v>
       </c>
-      <c r="F20" s="127">
+      <c r="F20" s="118">
         <v>190</v>
       </c>
-      <c r="G20" s="127">
+      <c r="G20" s="118">
         <v>248</v>
       </c>
-      <c r="H20" s="127">
+      <c r="H20" s="118">
         <v>198</v>
       </c>
-      <c r="I20" s="127">
+      <c r="I20" s="118">
         <v>148</v>
       </c>
-      <c r="J20" s="127">
+      <c r="J20" s="118">
         <v>96</v>
       </c>
-      <c r="K20" s="127">
-        <v>0</v>
-      </c>
-      <c r="L20" s="127">
-        <v>0</v>
-      </c>
-      <c r="M20" s="127">
+      <c r="K20" s="118">
+        <v>0</v>
+      </c>
+      <c r="L20" s="118">
+        <v>0</v>
+      </c>
+      <c r="M20" s="118">
         <v>0</v>
       </c>
       <c r="N20" s="82">
@@ -14058,13 +14244,13 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="114" t="s">
         <v>384</v>
       </c>
-      <c r="B21" s="128">
+      <c r="B21" s="119">
         <v>40001</v>
       </c>
-      <c r="C21" s="123" t="s">
+      <c r="C21" s="114" t="s">
         <v>385</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -14105,10 +14291,10 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="114" t="s">
         <v>386</v>
       </c>
-      <c r="C22" s="123" t="s">
+      <c r="C22" s="114" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -14149,10 +14335,10 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B23" s="128">
+      <c r="B23" s="119">
         <v>40003</v>
       </c>
-      <c r="C23" s="123" t="s">
+      <c r="C23" s="114" t="s">
         <v>387</v>
       </c>
       <c r="D23" s="9" t="s">
@@ -14193,40 +14379,40 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="128">
+      <c r="B24" s="119">
         <v>40005</v>
       </c>
-      <c r="C24" s="123" t="s">
+      <c r="C24" s="114" t="s">
         <v>388</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E24" s="127">
+      <c r="E24" s="118">
         <v>2000</v>
       </c>
-      <c r="F24" s="127">
+      <c r="F24" s="118">
         <v>2480</v>
       </c>
-      <c r="G24" s="127">
+      <c r="G24" s="118">
         <v>2270</v>
       </c>
-      <c r="H24" s="127">
+      <c r="H24" s="118">
         <v>2080</v>
       </c>
-      <c r="I24" s="127">
+      <c r="I24" s="118">
         <v>970</v>
       </c>
-      <c r="J24" s="127">
+      <c r="J24" s="118">
         <v>150</v>
       </c>
-      <c r="K24" s="127">
+      <c r="K24" s="118">
         <v>10</v>
       </c>
-      <c r="L24" s="127">
-        <v>0</v>
-      </c>
-      <c r="M24" s="127">
+      <c r="L24" s="118">
+        <v>0</v>
+      </c>
+      <c r="M24" s="118">
         <v>0</v>
       </c>
       <c r="N24" s="82">
@@ -14237,423 +14423,423 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="123">
+      <c r="B25" s="114">
         <v>40006</v>
       </c>
-      <c r="C25" s="123" t="s">
+      <c r="C25" s="114" t="s">
         <v>389</v>
       </c>
       <c r="D25" s="9">
         <v>0</v>
       </c>
-      <c r="E25" s="127">
-        <v>0</v>
-      </c>
-      <c r="F25" s="127">
+      <c r="E25" s="118">
+        <v>0</v>
+      </c>
+      <c r="F25" s="118">
         <v>-54</v>
       </c>
-      <c r="G25" s="127">
+      <c r="G25" s="118">
         <v>-103</v>
       </c>
-      <c r="H25" s="127">
+      <c r="H25" s="118">
         <v>-153</v>
       </c>
-      <c r="I25" s="127">
+      <c r="I25" s="118">
         <v>-198</v>
       </c>
-      <c r="J25" s="127">
+      <c r="J25" s="118">
         <v>-251</v>
       </c>
-      <c r="K25" s="127">
+      <c r="K25" s="118">
         <v>-326</v>
       </c>
-      <c r="L25" s="127">
+      <c r="L25" s="118">
         <v>-113</v>
       </c>
-      <c r="M25" s="127">
+      <c r="M25" s="118">
         <v>0</v>
       </c>
       <c r="N25" s="82"/>
       <c r="O25" s="82"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="123">
+      <c r="B26" s="114">
         <v>40008</v>
       </c>
-      <c r="C26" s="123" t="s">
+      <c r="C26" s="114" t="s">
         <v>390</v>
       </c>
       <c r="D26" s="9">
         <v>-64</v>
       </c>
-      <c r="E26" s="127">
+      <c r="E26" s="118">
         <v>-52</v>
       </c>
-      <c r="F26" s="127">
+      <c r="F26" s="118">
         <v>-44</v>
       </c>
-      <c r="G26" s="127">
+      <c r="G26" s="118">
         <v>-21</v>
       </c>
-      <c r="H26" s="127">
+      <c r="H26" s="118">
         <v>-12</v>
       </c>
-      <c r="I26" s="127">
-        <v>0</v>
-      </c>
-      <c r="J26" s="127">
-        <v>0</v>
-      </c>
-      <c r="K26" s="127">
-        <v>0</v>
-      </c>
-      <c r="L26" s="127">
-        <v>0</v>
-      </c>
-      <c r="M26" s="127">
+      <c r="I26" s="118">
+        <v>0</v>
+      </c>
+      <c r="J26" s="118">
+        <v>0</v>
+      </c>
+      <c r="K26" s="118">
+        <v>0</v>
+      </c>
+      <c r="L26" s="118">
+        <v>0</v>
+      </c>
+      <c r="M26" s="118">
         <v>0</v>
       </c>
       <c r="N26" s="82"/>
       <c r="O26" s="82"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B27" s="123">
+      <c r="B27" s="114">
         <v>40009</v>
       </c>
-      <c r="C27" s="123" t="s">
+      <c r="C27" s="114" t="s">
         <v>391</v>
       </c>
       <c r="D27" s="9">
         <v>0</v>
       </c>
-      <c r="E27" s="127">
+      <c r="E27" s="118">
         <v>-20</v>
       </c>
-      <c r="F27" s="127">
+      <c r="F27" s="118">
         <v>-50</v>
       </c>
-      <c r="G27" s="127">
+      <c r="G27" s="118">
         <v>-55</v>
       </c>
-      <c r="H27" s="127">
+      <c r="H27" s="118">
         <v>-25</v>
       </c>
-      <c r="I27" s="127">
-        <v>0</v>
-      </c>
-      <c r="J27" s="127">
-        <v>0</v>
-      </c>
-      <c r="K27" s="127">
-        <v>0</v>
-      </c>
-      <c r="L27" s="127">
-        <v>0</v>
-      </c>
-      <c r="M27" s="127">
+      <c r="I27" s="118">
+        <v>0</v>
+      </c>
+      <c r="J27" s="118">
+        <v>0</v>
+      </c>
+      <c r="K27" s="118">
+        <v>0</v>
+      </c>
+      <c r="L27" s="118">
+        <v>0</v>
+      </c>
+      <c r="M27" s="118">
         <v>0</v>
       </c>
       <c r="N27" s="82"/>
       <c r="O27" s="82"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="123">
+      <c r="B28" s="114">
         <v>40010</v>
       </c>
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="114" t="s">
         <v>392</v>
       </c>
       <c r="D28" s="9">
         <v>-1</v>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="118">
         <v>-47</v>
       </c>
-      <c r="F28" s="127">
+      <c r="F28" s="118">
         <v>-67</v>
       </c>
-      <c r="G28" s="127">
+      <c r="G28" s="118">
         <v>-49</v>
       </c>
-      <c r="H28" s="127">
+      <c r="H28" s="118">
         <v>-39</v>
       </c>
-      <c r="I28" s="127">
+      <c r="I28" s="118">
         <v>-5</v>
       </c>
-      <c r="J28" s="127">
-        <v>0</v>
-      </c>
-      <c r="K28" s="127">
-        <v>0</v>
-      </c>
-      <c r="L28" s="127">
-        <v>0</v>
-      </c>
-      <c r="M28" s="127">
+      <c r="J28" s="118">
+        <v>0</v>
+      </c>
+      <c r="K28" s="118">
+        <v>0</v>
+      </c>
+      <c r="L28" s="118">
+        <v>0</v>
+      </c>
+      <c r="M28" s="118">
         <v>0</v>
       </c>
       <c r="N28" s="82"/>
       <c r="O28" s="82"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="123">
+      <c r="B29" s="114">
         <v>40011</v>
       </c>
-      <c r="C29" s="123" t="s">
+      <c r="C29" s="114" t="s">
         <v>393</v>
       </c>
       <c r="D29" s="9">
         <v>0</v>
       </c>
-      <c r="E29" s="127">
-        <v>0</v>
-      </c>
-      <c r="F29" s="127">
-        <v>0</v>
-      </c>
-      <c r="G29" s="127">
+      <c r="E29" s="118">
+        <v>0</v>
+      </c>
+      <c r="F29" s="118">
+        <v>0</v>
+      </c>
+      <c r="G29" s="118">
         <v>-167</v>
       </c>
-      <c r="H29" s="127">
+      <c r="H29" s="118">
         <v>-163</v>
       </c>
-      <c r="I29" s="127">
+      <c r="I29" s="118">
         <v>-148</v>
       </c>
-      <c r="J29" s="127">
+      <c r="J29" s="118">
         <v>-133</v>
       </c>
-      <c r="K29" s="127">
+      <c r="K29" s="118">
         <v>-118</v>
       </c>
-      <c r="L29" s="127">
+      <c r="L29" s="118">
         <v>-74</v>
       </c>
-      <c r="M29" s="127">
+      <c r="M29" s="118">
         <v>0</v>
       </c>
       <c r="N29" s="82"/>
       <c r="O29" s="82"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="123" t="s">
+      <c r="A30" s="114" t="s">
         <v>394</v>
       </c>
-      <c r="B30" s="128">
+      <c r="B30" s="119">
         <v>50305</v>
       </c>
-      <c r="C30" s="123" t="s">
+      <c r="C30" s="114" t="s">
         <v>395</v>
       </c>
-      <c r="D30" s="130">
+      <c r="D30" s="121">
         <v>5</v>
       </c>
-      <c r="E30" s="130">
+      <c r="E30" s="121">
         <v>120</v>
       </c>
-      <c r="F30" s="130">
+      <c r="F30" s="121">
         <v>20</v>
       </c>
-      <c r="G30" s="130">
+      <c r="G30" s="121">
         <v>5</v>
       </c>
-      <c r="H30" s="130">
-        <v>0</v>
-      </c>
-      <c r="I30" s="130">
-        <v>0</v>
-      </c>
-      <c r="J30" s="130">
-        <v>0</v>
-      </c>
-      <c r="K30" s="130">
-        <v>0</v>
-      </c>
-      <c r="L30" s="130">
-        <v>0</v>
-      </c>
-      <c r="M30" s="130">
-        <v>0</v>
-      </c>
-      <c r="N30" s="131">
+      <c r="H30" s="121">
+        <v>0</v>
+      </c>
+      <c r="I30" s="121">
+        <v>0</v>
+      </c>
+      <c r="J30" s="121">
+        <v>0</v>
+      </c>
+      <c r="K30" s="121">
+        <v>0</v>
+      </c>
+      <c r="L30" s="121">
+        <v>0</v>
+      </c>
+      <c r="M30" s="121">
+        <v>0</v>
+      </c>
+      <c r="N30" s="122">
         <v>150</v>
       </c>
-      <c r="O30" s="131">
+      <c r="O30" s="122">
         <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="123"/>
-      <c r="B31" s="128">
+      <c r="A31" s="114"/>
+      <c r="B31" s="119">
         <v>50304</v>
       </c>
-      <c r="C31" s="123" t="s">
+      <c r="C31" s="114" t="s">
         <v>396</v>
       </c>
-      <c r="D31" s="130">
+      <c r="D31" s="121">
         <v>-79</v>
       </c>
-      <c r="E31" s="130">
+      <c r="E31" s="121">
         <v>-65</v>
       </c>
-      <c r="F31" s="130">
+      <c r="F31" s="121">
         <v>-46</v>
       </c>
-      <c r="G31" s="130">
+      <c r="G31" s="121">
         <v>-38</v>
       </c>
-      <c r="H31" s="130">
+      <c r="H31" s="121">
         <v>-27</v>
       </c>
-      <c r="I31" s="130">
+      <c r="I31" s="121">
         <v>-21</v>
       </c>
-      <c r="J31" s="130">
+      <c r="J31" s="121">
         <v>-3</v>
       </c>
-      <c r="K31" s="130">
-        <v>0</v>
-      </c>
-      <c r="L31" s="130">
-        <v>0</v>
-      </c>
-      <c r="M31" s="130">
-        <v>0</v>
-      </c>
-      <c r="N31" s="131"/>
-      <c r="O31" s="131"/>
+      <c r="K31" s="121">
+        <v>0</v>
+      </c>
+      <c r="L31" s="121">
+        <v>0</v>
+      </c>
+      <c r="M31" s="121">
+        <v>0</v>
+      </c>
+      <c r="N31" s="122"/>
+      <c r="O31" s="122"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B32" s="128">
+      <c r="B32" s="119">
         <v>50401</v>
       </c>
-      <c r="C32" s="123" t="s">
+      <c r="C32" s="114" t="s">
         <v>397</v>
       </c>
-      <c r="D32" s="132">
-        <v>0</v>
-      </c>
-      <c r="E32" s="132">
+      <c r="D32" s="123">
+        <v>0</v>
+      </c>
+      <c r="E32" s="123">
         <v>396</v>
       </c>
-      <c r="F32" s="132">
+      <c r="F32" s="123">
         <v>291</v>
       </c>
-      <c r="G32" s="132">
+      <c r="G32" s="123">
         <v>65</v>
       </c>
-      <c r="H32" s="132">
+      <c r="H32" s="123">
         <v>44</v>
       </c>
-      <c r="I32" s="132">
+      <c r="I32" s="123">
         <v>33</v>
       </c>
-      <c r="J32" s="132">
+      <c r="J32" s="123">
         <v>21</v>
       </c>
-      <c r="K32" s="132">
-        <v>0</v>
-      </c>
-      <c r="L32" s="132">
-        <v>0</v>
-      </c>
-      <c r="M32" s="132">
-        <v>0</v>
-      </c>
-      <c r="N32" s="131">
+      <c r="K32" s="123">
+        <v>0</v>
+      </c>
+      <c r="L32" s="123">
+        <v>0</v>
+      </c>
+      <c r="M32" s="123">
+        <v>0</v>
+      </c>
+      <c r="N32" s="122">
         <v>796</v>
       </c>
-      <c r="O32" s="131">
+      <c r="O32" s="122">
         <v>850</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="128">
+      <c r="B33" s="119">
         <v>50402</v>
       </c>
-      <c r="C33" s="123" t="s">
+      <c r="C33" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D33" s="132">
+      <c r="D33" s="123">
         <v>-89</v>
       </c>
-      <c r="E33" s="132">
+      <c r="E33" s="123">
         <v>-489</v>
       </c>
-      <c r="F33" s="132">
+      <c r="F33" s="123">
         <v>-1036</v>
       </c>
-      <c r="G33" s="132">
+      <c r="G33" s="123">
         <v>-1302</v>
       </c>
-      <c r="H33" s="132">
+      <c r="H33" s="123">
         <v>-1203</v>
       </c>
-      <c r="I33" s="132">
+      <c r="I33" s="123">
         <v>-1151</v>
       </c>
-      <c r="J33" s="132">
+      <c r="J33" s="123">
         <v>-899</v>
       </c>
-      <c r="K33" s="132">
+      <c r="K33" s="123">
         <v>-332</v>
       </c>
-      <c r="L33" s="132">
+      <c r="L33" s="123">
         <v>-291</v>
       </c>
-      <c r="M33" s="132">
+      <c r="M33" s="123">
         <v>-290</v>
       </c>
-      <c r="N33" s="131"/>
-      <c r="O33" s="131"/>
+      <c r="N33" s="122"/>
+      <c r="O33" s="122"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="128">
+      <c r="B34" s="119">
         <v>50403</v>
       </c>
-      <c r="C34" s="123" t="s">
+      <c r="C34" s="114" t="s">
         <v>399</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E34" s="127">
+      <c r="E34" s="118">
         <v>10</v>
       </c>
-      <c r="F34" s="127">
+      <c r="F34" s="118">
         <v>60</v>
       </c>
-      <c r="G34" s="127">
+      <c r="G34" s="118">
         <v>130</v>
       </c>
-      <c r="H34" s="127">
+      <c r="H34" s="118">
         <v>210</v>
       </c>
-      <c r="I34" s="127">
+      <c r="I34" s="118">
         <v>200</v>
       </c>
-      <c r="J34" s="127">
+      <c r="J34" s="118">
         <v>130</v>
       </c>
-      <c r="K34" s="127">
+      <c r="K34" s="118">
         <v>60</v>
       </c>
-      <c r="L34" s="127">
+      <c r="L34" s="118">
         <v>20</v>
       </c>
-      <c r="M34" s="127">
-        <v>0</v>
-      </c>
-      <c r="N34" s="131">
+      <c r="M34" s="118">
+        <v>0</v>
+      </c>
+      <c r="N34" s="122">
         <v>410</v>
       </c>
-      <c r="O34" s="131">
+      <c r="O34" s="122">
         <v>820</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="128">
+      <c r="B35" s="119">
         <v>50404</v>
       </c>
       <c r="C35" s="17" t="s">
@@ -14689,93 +14875,93 @@
       <c r="M35" s="9">
         <v>0</v>
       </c>
-      <c r="N35" s="131">
+      <c r="N35" s="122">
         <v>147</v>
       </c>
-      <c r="O35" s="131">
+      <c r="O35" s="122">
         <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B36" s="128">
+      <c r="B36" s="119">
         <v>50501</v>
       </c>
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="114" t="s">
         <v>401</v>
       </c>
-      <c r="D36" s="127">
+      <c r="D36" s="118">
         <v>7</v>
       </c>
-      <c r="E36" s="127">
+      <c r="E36" s="118">
         <v>43</v>
       </c>
-      <c r="F36" s="127">
+      <c r="F36" s="118">
         <v>202</v>
       </c>
-      <c r="G36" s="127">
+      <c r="G36" s="118">
         <v>177</v>
       </c>
-      <c r="H36" s="127">
+      <c r="H36" s="118">
         <v>202</v>
       </c>
-      <c r="I36" s="127">
+      <c r="I36" s="118">
         <v>104</v>
       </c>
-      <c r="J36" s="127">
+      <c r="J36" s="118">
         <v>105</v>
       </c>
-      <c r="K36" s="127">
+      <c r="K36" s="118">
         <v>105</v>
       </c>
-      <c r="L36" s="127">
+      <c r="L36" s="118">
         <v>55</v>
       </c>
-      <c r="M36" s="127">
-        <v>0</v>
-      </c>
-      <c r="N36" s="131">
+      <c r="M36" s="118">
+        <v>0</v>
+      </c>
+      <c r="N36" s="122">
         <v>631</v>
       </c>
-      <c r="O36" s="131">
+      <c r="O36" s="122">
         <v>1000</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="123" t="s">
+      <c r="A37" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="B37" s="128"/>
+      <c r="B37" s="119"/>
       <c r="C37" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="D37" s="133">
+      <c r="D37" s="124">
         <v>-857</v>
       </c>
-      <c r="E37" s="130">
+      <c r="E37" s="121">
         <v>-936</v>
       </c>
-      <c r="F37" s="130">
+      <c r="F37" s="121">
         <v>-1237</v>
       </c>
-      <c r="G37" s="130">
+      <c r="G37" s="121">
         <v>-887</v>
       </c>
-      <c r="H37" s="130">
+      <c r="H37" s="121">
         <v>-570</v>
       </c>
-      <c r="I37" s="130">
+      <c r="I37" s="121">
         <v>-360</v>
       </c>
-      <c r="J37" s="130">
+      <c r="J37" s="121">
         <v>-112</v>
       </c>
-      <c r="K37" s="130" t="s">
+      <c r="K37" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="L37" s="130" t="s">
+      <c r="L37" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="M37" s="130" t="s">
+      <c r="M37" s="121" t="s">
         <v>181</v>
       </c>
       <c r="N37" s="82">
@@ -14786,10 +14972,10 @@
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="123" t="s">
+      <c r="A38" s="114" t="s">
         <v>404</v>
       </c>
-      <c r="B38" s="128">
+      <c r="B38" s="119">
         <v>71121</v>
       </c>
       <c r="C38" s="17" t="s">
@@ -14833,11 +15019,11 @@
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="123"/>
-      <c r="B39" s="128">
+      <c r="A39" s="114"/>
+      <c r="B39" s="119">
         <v>71401</v>
       </c>
-      <c r="C39" s="123" t="s">
+      <c r="C39" s="114" t="s">
         <v>406</v>
       </c>
       <c r="D39" s="9">
@@ -14878,43 +15064,43 @@
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="123" t="s">
+      <c r="A40" s="114" t="s">
         <v>407</v>
       </c>
-      <c r="B40" s="128">
+      <c r="B40" s="119">
         <v>82005</v>
       </c>
-      <c r="C40" s="123" t="s">
+      <c r="C40" s="114" t="s">
         <v>408</v>
       </c>
-      <c r="D40" s="127">
+      <c r="D40" s="118">
         <v>50</v>
       </c>
-      <c r="E40" s="127">
+      <c r="E40" s="118">
         <v>300</v>
       </c>
-      <c r="F40" s="127">
+      <c r="F40" s="118">
         <v>450</v>
       </c>
-      <c r="G40" s="127">
+      <c r="G40" s="118">
         <v>200</v>
       </c>
-      <c r="H40" s="127">
-        <v>0</v>
-      </c>
-      <c r="I40" s="127">
-        <v>0</v>
-      </c>
-      <c r="J40" s="127">
-        <v>0</v>
-      </c>
-      <c r="K40" s="127">
-        <v>0</v>
-      </c>
-      <c r="L40" s="127">
-        <v>0</v>
-      </c>
-      <c r="M40" s="127">
+      <c r="H40" s="118">
+        <v>0</v>
+      </c>
+      <c r="I40" s="118">
+        <v>0</v>
+      </c>
+      <c r="J40" s="118">
+        <v>0</v>
+      </c>
+      <c r="K40" s="118">
+        <v>0</v>
+      </c>
+      <c r="L40" s="118">
+        <v>0</v>
+      </c>
+      <c r="M40" s="118">
         <v>0</v>
       </c>
       <c r="N40" s="82">
@@ -14925,40 +15111,40 @@
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="128">
+      <c r="B41" s="119">
         <v>83003</v>
       </c>
-      <c r="C41" s="123" t="s">
+      <c r="C41" s="114" t="s">
         <v>409</v>
       </c>
-      <c r="D41" s="127">
-        <v>0</v>
-      </c>
-      <c r="E41" s="127">
+      <c r="D41" s="118">
+        <v>0</v>
+      </c>
+      <c r="E41" s="118">
         <v>2730</v>
       </c>
-      <c r="F41" s="127">
+      <c r="F41" s="118">
         <v>7665</v>
       </c>
-      <c r="G41" s="127">
+      <c r="G41" s="118">
         <v>105</v>
       </c>
-      <c r="H41" s="127">
-        <v>0</v>
-      </c>
-      <c r="I41" s="127">
-        <v>0</v>
-      </c>
-      <c r="J41" s="127">
-        <v>0</v>
-      </c>
-      <c r="K41" s="127">
-        <v>0</v>
-      </c>
-      <c r="L41" s="127">
-        <v>0</v>
-      </c>
-      <c r="M41" s="127">
+      <c r="H41" s="118">
+        <v>0</v>
+      </c>
+      <c r="I41" s="118">
+        <v>0</v>
+      </c>
+      <c r="J41" s="118">
+        <v>0</v>
+      </c>
+      <c r="K41" s="118">
+        <v>0</v>
+      </c>
+      <c r="L41" s="118">
+        <v>0</v>
+      </c>
+      <c r="M41" s="118">
         <v>0</v>
       </c>
       <c r="N41" s="82">
@@ -14969,40 +15155,40 @@
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="128">
+      <c r="B42" s="119">
         <v>86001</v>
       </c>
-      <c r="C42" s="123" t="s">
+      <c r="C42" s="114" t="s">
         <v>410</v>
       </c>
-      <c r="D42" s="127">
+      <c r="D42" s="118">
         <v>1</v>
       </c>
-      <c r="E42" s="127">
+      <c r="E42" s="118">
         <v>25</v>
       </c>
-      <c r="F42" s="127">
+      <c r="F42" s="118">
         <v>14</v>
       </c>
-      <c r="G42" s="127">
-        <v>0</v>
-      </c>
-      <c r="H42" s="127">
-        <v>0</v>
-      </c>
-      <c r="I42" s="127">
-        <v>0</v>
-      </c>
-      <c r="J42" s="127">
-        <v>0</v>
-      </c>
-      <c r="K42" s="127">
-        <v>0</v>
-      </c>
-      <c r="L42" s="127">
-        <v>0</v>
-      </c>
-      <c r="M42" s="127">
+      <c r="G42" s="118">
+        <v>0</v>
+      </c>
+      <c r="H42" s="118">
+        <v>0</v>
+      </c>
+      <c r="I42" s="118">
+        <v>0</v>
+      </c>
+      <c r="J42" s="118">
+        <v>0</v>
+      </c>
+      <c r="K42" s="118">
+        <v>0</v>
+      </c>
+      <c r="L42" s="118">
+        <v>0</v>
+      </c>
+      <c r="M42" s="118">
         <v>0</v>
       </c>
       <c r="N42" s="82">
@@ -15013,40 +15199,40 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="128">
+      <c r="B43" s="119">
         <v>87001</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="D43" s="127">
-        <v>0</v>
-      </c>
-      <c r="E43" s="127">
+      <c r="D43" s="118">
+        <v>0</v>
+      </c>
+      <c r="E43" s="118">
         <v>150</v>
       </c>
-      <c r="F43" s="127">
+      <c r="F43" s="118">
         <v>117</v>
       </c>
-      <c r="G43" s="127">
+      <c r="G43" s="118">
         <v>24</v>
       </c>
-      <c r="H43" s="127">
+      <c r="H43" s="118">
         <v>6</v>
       </c>
-      <c r="I43" s="127">
+      <c r="I43" s="118">
         <v>1</v>
       </c>
-      <c r="J43" s="127">
-        <v>0</v>
-      </c>
-      <c r="K43" s="127">
-        <v>0</v>
-      </c>
-      <c r="L43" s="127">
-        <v>0</v>
-      </c>
-      <c r="M43" s="127">
+      <c r="J43" s="118">
+        <v>0</v>
+      </c>
+      <c r="K43" s="118">
+        <v>0</v>
+      </c>
+      <c r="L43" s="118">
+        <v>0</v>
+      </c>
+      <c r="M43" s="118">
         <v>0</v>
       </c>
       <c r="N43" s="82">
@@ -15057,43 +15243,43 @@
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="123" t="s">
+      <c r="A44" s="114" t="s">
         <v>412</v>
       </c>
-      <c r="B44" s="128">
+      <c r="B44" s="119">
         <v>90001</v>
       </c>
-      <c r="C44" s="123" t="s">
+      <c r="C44" s="114" t="s">
         <v>413</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="127">
+      <c r="E44" s="118">
         <v>780</v>
       </c>
-      <c r="F44" s="127">
+      <c r="F44" s="118">
         <v>2260</v>
       </c>
-      <c r="G44" s="127">
+      <c r="G44" s="118">
         <v>4520</v>
       </c>
-      <c r="H44" s="127">
+      <c r="H44" s="118">
         <v>7033</v>
       </c>
-      <c r="I44" s="127">
+      <c r="I44" s="118">
         <v>8715</v>
       </c>
-      <c r="J44" s="127">
+      <c r="J44" s="118">
         <v>8668</v>
       </c>
-      <c r="K44" s="127">
+      <c r="K44" s="118">
         <v>6731</v>
       </c>
-      <c r="L44" s="127">
+      <c r="L44" s="118">
         <v>4050</v>
       </c>
-      <c r="M44" s="127">
+      <c r="M44" s="118">
         <v>1927</v>
       </c>
       <c r="N44" s="82">
@@ -15104,40 +15290,40 @@
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B45" s="128">
+      <c r="B45" s="119">
         <v>90002</v>
       </c>
-      <c r="C45" s="123" t="s">
+      <c r="C45" s="114" t="s">
         <v>414</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E45" s="127">
+      <c r="E45" s="118">
         <v>540</v>
       </c>
-      <c r="F45" s="127">
+      <c r="F45" s="118">
         <v>1327</v>
       </c>
-      <c r="G45" s="127">
+      <c r="G45" s="118">
         <v>2191</v>
       </c>
-      <c r="H45" s="127">
+      <c r="H45" s="118">
         <v>2868</v>
       </c>
-      <c r="I45" s="127">
+      <c r="I45" s="118">
         <v>2882</v>
       </c>
-      <c r="J45" s="127">
+      <c r="J45" s="118">
         <v>1171</v>
       </c>
-      <c r="K45" s="127">
+      <c r="K45" s="118">
         <v>573</v>
       </c>
-      <c r="L45" s="127">
+      <c r="L45" s="118">
         <v>281</v>
       </c>
-      <c r="M45" s="127">
+      <c r="M45" s="118">
         <v>175</v>
       </c>
       <c r="N45" s="82">
@@ -15148,40 +15334,40 @@
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B46" s="128">
+      <c r="B46" s="119">
         <v>90003</v>
       </c>
-      <c r="C46" s="123" t="s">
+      <c r="C46" s="114" t="s">
         <v>415</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E46" s="127">
+      <c r="E46" s="118">
         <v>4000</v>
       </c>
-      <c r="F46" s="127">
+      <c r="F46" s="118">
         <v>6900</v>
       </c>
-      <c r="G46" s="127">
+      <c r="G46" s="118">
         <v>9550</v>
       </c>
-      <c r="H46" s="127">
+      <c r="H46" s="118">
         <v>11500</v>
       </c>
-      <c r="I46" s="127">
+      <c r="I46" s="118">
         <v>7050</v>
       </c>
-      <c r="J46" s="127">
+      <c r="J46" s="118">
         <v>4200</v>
       </c>
-      <c r="K46" s="127">
+      <c r="K46" s="118">
         <v>1800</v>
       </c>
-      <c r="L46" s="127">
-        <v>0</v>
-      </c>
-      <c r="M46" s="127">
+      <c r="L46" s="118">
+        <v>0</v>
+      </c>
+      <c r="M46" s="118">
         <v>0</v>
       </c>
       <c r="N46" s="82">
@@ -15192,40 +15378,40 @@
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B47" s="128">
+      <c r="B47" s="119">
         <v>90004</v>
       </c>
-      <c r="C47" s="123" t="s">
+      <c r="C47" s="114" t="s">
         <v>416</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E47" s="127">
+      <c r="E47" s="118">
         <v>189</v>
       </c>
-      <c r="F47" s="127">
+      <c r="F47" s="118">
         <v>528</v>
       </c>
-      <c r="G47" s="127">
+      <c r="G47" s="118">
         <v>967</v>
       </c>
-      <c r="H47" s="127">
+      <c r="H47" s="118">
         <v>1365</v>
       </c>
-      <c r="I47" s="127">
+      <c r="I47" s="118">
         <v>1330</v>
       </c>
-      <c r="J47" s="127">
+      <c r="J47" s="118">
         <v>1013</v>
       </c>
-      <c r="K47" s="127">
+      <c r="K47" s="118">
         <v>565</v>
       </c>
-      <c r="L47" s="127">
+      <c r="L47" s="118">
         <v>187</v>
       </c>
-      <c r="M47" s="127">
+      <c r="M47" s="118">
         <v>24</v>
       </c>
       <c r="N47" s="82">
@@ -15236,40 +15422,40 @@
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B48" s="128">
+      <c r="B48" s="119">
         <v>90005</v>
       </c>
-      <c r="C48" s="123" t="s">
+      <c r="C48" s="114" t="s">
         <v>417</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E48" s="127">
+      <c r="E48" s="118">
         <v>819</v>
       </c>
-      <c r="F48" s="127">
+      <c r="F48" s="118">
         <v>4180</v>
       </c>
-      <c r="G48" s="127">
+      <c r="G48" s="118">
         <v>5174</v>
       </c>
-      <c r="H48" s="127">
+      <c r="H48" s="118">
         <v>1976</v>
       </c>
-      <c r="I48" s="127">
+      <c r="I48" s="118">
         <v>358</v>
       </c>
-      <c r="J48" s="127">
+      <c r="J48" s="118">
         <v>54</v>
       </c>
-      <c r="K48" s="127">
+      <c r="K48" s="118">
         <v>12</v>
       </c>
-      <c r="L48" s="127">
+      <c r="L48" s="118">
         <v>2</v>
       </c>
-      <c r="M48" s="127">
+      <c r="M48" s="118">
         <v>0</v>
       </c>
       <c r="N48" s="82">
@@ -15280,40 +15466,40 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B49" s="128">
+      <c r="B49" s="119">
         <v>90006</v>
       </c>
-      <c r="C49" s="123" t="s">
+      <c r="C49" s="114" t="s">
         <v>418</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E49" s="127">
+      <c r="E49" s="118">
         <v>11</v>
       </c>
-      <c r="F49" s="127">
+      <c r="F49" s="118">
         <v>74</v>
       </c>
-      <c r="G49" s="127">
+      <c r="G49" s="118">
         <v>106</v>
       </c>
-      <c r="H49" s="127">
+      <c r="H49" s="118">
         <v>84</v>
       </c>
-      <c r="I49" s="127">
+      <c r="I49" s="118">
         <v>21</v>
       </c>
-      <c r="J49" s="127">
+      <c r="J49" s="118">
         <v>4</v>
       </c>
-      <c r="K49" s="127">
-        <v>0</v>
-      </c>
-      <c r="L49" s="127">
-        <v>0</v>
-      </c>
-      <c r="M49" s="127">
+      <c r="K49" s="118">
+        <v>0</v>
+      </c>
+      <c r="L49" s="118">
+        <v>0</v>
+      </c>
+      <c r="M49" s="118">
         <v>0</v>
       </c>
       <c r="N49" s="82">
@@ -15324,40 +15510,40 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B50" s="128">
+      <c r="B50" s="119">
         <v>90007</v>
       </c>
-      <c r="C50" s="123" t="s">
+      <c r="C50" s="114" t="s">
         <v>419</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E50" s="127">
+      <c r="E50" s="118">
         <v>3139</v>
       </c>
-      <c r="F50" s="127">
+      <c r="F50" s="118">
         <v>3020</v>
       </c>
-      <c r="G50" s="127">
+      <c r="G50" s="118">
         <v>2911</v>
       </c>
-      <c r="H50" s="127">
+      <c r="H50" s="118">
         <v>762</v>
       </c>
-      <c r="I50" s="127">
+      <c r="I50" s="118">
         <v>168</v>
       </c>
-      <c r="J50" s="127">
-        <v>0</v>
-      </c>
-      <c r="K50" s="127">
-        <v>0</v>
-      </c>
-      <c r="L50" s="127">
-        <v>0</v>
-      </c>
-      <c r="M50" s="127">
+      <c r="J50" s="118">
+        <v>0</v>
+      </c>
+      <c r="K50" s="118">
+        <v>0</v>
+      </c>
+      <c r="L50" s="118">
+        <v>0</v>
+      </c>
+      <c r="M50" s="118">
         <v>0</v>
       </c>
       <c r="N50" s="82">
@@ -15368,40 +15554,40 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B51" s="128">
+      <c r="B51" s="119">
         <v>90101</v>
       </c>
-      <c r="C51" s="123" t="s">
+      <c r="C51" s="114" t="s">
         <v>420</v>
       </c>
       <c r="D51" s="9">
         <v>0</v>
       </c>
-      <c r="E51" s="127">
+      <c r="E51" s="118">
         <v>-7</v>
       </c>
-      <c r="F51" s="127">
+      <c r="F51" s="118">
         <v>-64</v>
       </c>
-      <c r="G51" s="127">
+      <c r="G51" s="118">
         <v>-137</v>
       </c>
-      <c r="H51" s="127">
+      <c r="H51" s="118">
         <v>-204</v>
       </c>
-      <c r="I51" s="127">
+      <c r="I51" s="118">
         <v>-272</v>
       </c>
-      <c r="J51" s="127">
+      <c r="J51" s="118">
         <v>-333</v>
       </c>
-      <c r="K51" s="127">
+      <c r="K51" s="118">
         <v>-338</v>
       </c>
-      <c r="L51" s="127">
+      <c r="L51" s="118">
         <v>-331</v>
       </c>
-      <c r="M51" s="127">
+      <c r="M51" s="118">
         <v>-324</v>
       </c>
       <c r="N51" s="82">
@@ -15412,7 +15598,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B52" s="128">
+      <c r="B52" s="119">
         <v>90102</v>
       </c>
       <c r="C52" t="s">
@@ -15421,31 +15607,31 @@
       <c r="D52" s="9">
         <v>0</v>
       </c>
-      <c r="E52" s="127">
+      <c r="E52" s="118">
         <v>15</v>
       </c>
-      <c r="F52" s="127">
+      <c r="F52" s="118">
         <v>15</v>
       </c>
-      <c r="G52" s="127">
+      <c r="G52" s="118">
         <v>10</v>
       </c>
-      <c r="H52" s="127">
+      <c r="H52" s="118">
         <v>10</v>
       </c>
-      <c r="I52" s="127">
+      <c r="I52" s="118">
         <v>10</v>
       </c>
-      <c r="J52" s="127">
+      <c r="J52" s="118">
         <v>10</v>
       </c>
-      <c r="K52" s="127">
+      <c r="K52" s="118">
         <v>8</v>
       </c>
-      <c r="L52" s="127">
+      <c r="L52" s="118">
         <v>5</v>
       </c>
-      <c r="M52" s="127">
+      <c r="M52" s="118">
         <v>3</v>
       </c>
       <c r="N52" s="82">
@@ -15456,7 +15642,7 @@
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B53" s="128">
+      <c r="B53" s="119">
         <v>90103</v>
       </c>
       <c r="C53" s="17" t="s">
@@ -15465,31 +15651,31 @@
       <c r="D53" s="17">
         <v>5</v>
       </c>
-      <c r="E53" s="127">
+      <c r="E53" s="118">
         <v>25</v>
       </c>
-      <c r="F53" s="127">
+      <c r="F53" s="118">
         <v>25</v>
       </c>
-      <c r="G53" s="127">
+      <c r="G53" s="118">
         <v>25</v>
       </c>
-      <c r="H53" s="127">
+      <c r="H53" s="118">
         <v>20</v>
       </c>
-      <c r="I53" s="127">
-        <v>0</v>
-      </c>
-      <c r="J53" s="127">
-        <v>0</v>
-      </c>
-      <c r="K53" s="127">
-        <v>0</v>
-      </c>
-      <c r="L53" s="127">
-        <v>0</v>
-      </c>
-      <c r="M53" s="127">
+      <c r="I53" s="118">
+        <v>0</v>
+      </c>
+      <c r="J53" s="118">
+        <v>0</v>
+      </c>
+      <c r="K53" s="118">
+        <v>0</v>
+      </c>
+      <c r="L53" s="118">
+        <v>0</v>
+      </c>
+      <c r="M53" s="118">
         <v>0</v>
       </c>
       <c r="N53" s="82">
@@ -15500,13 +15686,13 @@
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" s="123" t="s">
+      <c r="A54" s="114" t="s">
         <v>423</v>
       </c>
-      <c r="B54" s="128">
+      <c r="B54" s="119">
         <v>100051</v>
       </c>
-      <c r="C54" s="123" t="s">
+      <c r="C54" s="114" t="s">
         <v>424</v>
       </c>
       <c r="D54" s="9" t="s">
@@ -15547,10 +15733,10 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B55" s="128">
+      <c r="B55" s="119">
         <v>100052</v>
       </c>
-      <c r="C55" s="123" t="s">
+      <c r="C55" s="114" t="s">
         <v>425</v>
       </c>
       <c r="D55" s="9" t="s">
@@ -15591,10 +15777,10 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B56" s="128">
+      <c r="B56" s="119">
         <v>100053</v>
       </c>
-      <c r="C56" s="123" t="s">
+      <c r="C56" s="114" t="s">
         <v>426</v>
       </c>
       <c r="D56" s="9" t="s">
@@ -15635,10 +15821,10 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B57" s="128">
+      <c r="B57" s="119">
         <v>100054</v>
       </c>
-      <c r="C57" s="123" t="s">
+      <c r="C57" s="114" t="s">
         <v>427</v>
       </c>
       <c r="D57" s="9" t="s">
@@ -15679,7 +15865,7 @@
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B58" s="128">
+      <c r="B58" s="119">
         <v>100055</v>
       </c>
       <c r="C58" s="17" t="s">
@@ -15723,10 +15909,10 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B59" s="128">
+      <c r="B59" s="119">
         <v>100056</v>
       </c>
-      <c r="C59" s="123" t="s">
+      <c r="C59" s="114" t="s">
         <v>429</v>
       </c>
       <c r="D59" s="9" t="s">
@@ -15767,7 +15953,7 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B60" s="128">
+      <c r="B60" s="119">
         <v>100057</v>
       </c>
       <c r="C60" s="17" t="s">
@@ -15811,10 +15997,10 @@
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B61" s="128">
+      <c r="B61" s="119">
         <v>100101</v>
       </c>
-      <c r="C61" s="123" t="s">
+      <c r="C61" s="114" t="s">
         <v>431</v>
       </c>
       <c r="D61" s="9" t="s">
@@ -15855,7 +16041,7 @@
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B62" s="128">
+      <c r="B62" s="119">
         <v>100102</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -15899,10 +16085,10 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B63" s="128">
+      <c r="B63" s="119">
         <v>100202</v>
       </c>
-      <c r="C63" s="123" t="s">
+      <c r="C63" s="114" t="s">
         <v>433</v>
       </c>
       <c r="D63" s="9">
@@ -15943,40 +16129,40 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B64" s="128">
+      <c r="B64" s="119">
         <v>100203</v>
       </c>
-      <c r="C64" s="123" t="s">
+      <c r="C64" s="114" t="s">
         <v>434</v>
       </c>
       <c r="D64" s="9">
         <v>0</v>
       </c>
-      <c r="E64" s="127">
+      <c r="E64" s="118">
         <v>50</v>
       </c>
-      <c r="F64" s="127">
+      <c r="F64" s="118">
         <v>150</v>
       </c>
-      <c r="G64" s="127">
+      <c r="G64" s="118">
         <v>275</v>
       </c>
-      <c r="H64" s="127">
+      <c r="H64" s="118">
         <v>300</v>
       </c>
-      <c r="I64" s="127">
+      <c r="I64" s="118">
         <v>150</v>
       </c>
-      <c r="J64" s="127">
+      <c r="J64" s="118">
         <v>100</v>
       </c>
-      <c r="K64" s="127">
+      <c r="K64" s="118">
         <v>100</v>
       </c>
-      <c r="L64" s="127">
+      <c r="L64" s="118">
         <v>100</v>
       </c>
-      <c r="M64" s="127">
+      <c r="M64" s="118">
         <v>100</v>
       </c>
       <c r="N64" s="82">
@@ -15987,38 +16173,38 @@
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B65" s="128">
+      <c r="B65" s="119">
         <v>100204</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>435</v>
       </c>
       <c r="D65" s="9"/>
-      <c r="E65" s="127">
+      <c r="E65" s="118">
         <v>25</v>
       </c>
-      <c r="F65" s="127">
+      <c r="F65" s="118">
         <v>100</v>
       </c>
-      <c r="G65" s="127">
+      <c r="G65" s="118">
         <v>225</v>
       </c>
-      <c r="H65" s="127">
+      <c r="H65" s="118">
         <v>350</v>
       </c>
-      <c r="I65" s="127">
+      <c r="I65" s="118">
         <v>200</v>
       </c>
-      <c r="J65" s="127">
-        <v>0</v>
-      </c>
-      <c r="K65" s="127">
-        <v>0</v>
-      </c>
-      <c r="L65" s="127">
-        <v>0</v>
-      </c>
-      <c r="M65" s="127">
+      <c r="J65" s="118">
+        <v>0</v>
+      </c>
+      <c r="K65" s="118">
+        <v>0</v>
+      </c>
+      <c r="L65" s="118">
+        <v>0</v>
+      </c>
+      <c r="M65" s="118">
         <v>0</v>
       </c>
       <c r="N65" s="82">
@@ -16029,7 +16215,7 @@
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C66" s="135" t="s">
+      <c r="C66" s="126" t="s">
         <v>436</v>
       </c>
       <c r="D66" s="81">
@@ -16076,14 +16262,14 @@
       <c r="O66" s="81"/>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C67" s="135" t="s">
+      <c r="C67" s="126" t="s">
         <v>437</v>
       </c>
-      <c r="D67" s="120">
+      <c r="D67" s="113">
         <f>D66/1000</f>
         <v>0.51700000000000002</v>
       </c>
-      <c r="E67" s="120">
+      <c r="E67" s="113">
         <f t="shared" ref="E67:M67" si="1">E66/1000</f>
         <v>56.976999999999997</v>
       </c>
@@ -16145,19 +16331,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="F1" s="112" t="s">
+      <c r="F1" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -16207,29 +16393,28 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" s="121" t="s">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121" t="s">
+      <c r="C3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="121" t="s">
+      <c r="D3" t="s">
         <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="119">
-        <v>0</v>
-      </c>
-      <c r="G3" s="136">
+      <c r="F3" s="112">
+        <v>0</v>
+      </c>
+      <c r="G3" s="127">
         <v>-7961</v>
       </c>
-      <c r="H3" s="136">
+      <c r="H3" s="127">
         <v>-16116</v>
       </c>
-      <c r="I3" s="136">
+      <c r="I3" s="127">
         <v>-21645</v>
       </c>
       <c r="J3" s="15">
@@ -18270,20 +18455,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="128" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
     </row>
     <row r="2" spans="1:15" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -19900,7 +20085,7 @@
       <c r="A8" s="13"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="13" t="s">
         <v>361</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -19968,20 +20153,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="128" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
     </row>
     <row r="2" spans="1:15" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -21736,19 +21921,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -23595,14 +23780,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="E1" s="114" t="s">
+      <c r="E1" s="130" t="s">
         <v>206</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -24600,19 +24785,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -26930,15 +27115,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="131" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
       <c r="H2" s="43"/>
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
@@ -26969,18 +27154,18 @@
       <c r="A4" s="42"/>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="133" t="s">
         <v>272</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
       <c r="N4" s="56"/>
       <c r="O4" s="56"/>
     </row>
@@ -27311,10 +27496,10 @@
       <c r="B15" s="49">
         <v>70511</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="132" t="s">
         <v>279</v>
       </c>
-      <c r="D15" s="116"/>
+      <c r="D15" s="132"/>
       <c r="E15" s="48"/>
       <c r="F15" s="48"/>
       <c r="G15" s="48"/>
@@ -27986,6 +28171,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0a02388e-6178-4513-9b82-88b9dc6bf457}" enabled="0" method="" siteId="{0a02388e-6178-4513-9b82-88b9dc6bf457}" removed="1"/>
+  <clbl:label id="{a6274e99-f707-4183-90a3-28f81526dfab}" enabled="1" method="Standard" siteId="{0a02388e-6178-4513-9b82-88b9dc6bf457}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>